--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487489_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487489_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3535</v>
+        <v>8.183999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.076700000000001</v>
+        <v>8.2814</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2768</v>
+        <v>-0.0974</v>
       </c>
       <c r="G2" t="n">
         <v>3.1796</v>
@@ -610,13 +610,13 @@
         <v>2.9377</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5645</v>
+        <v>0.3949</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2682</v>
+        <v>-0.0635</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8327</v>
+        <v>0.4585</v>
       </c>
       <c r="V2" t="n">
         <v>2.651</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7871</v>
+        <v>0.8497</v>
       </c>
       <c r="E3" t="n">
-        <v>1.189</v>
+        <v>0.9843</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.402</v>
+        <v>-0.1346</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3624</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4029</v>
+        <v>0.4655</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4734</v>
+        <v>0.2688</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0706</v>
+        <v>0.1967</v>
       </c>
       <c r="V3" t="n">
         <v>0.5507</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2981</v>
+        <v>-1.0106</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2712</v>
+        <v>-0.4759</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0268</v>
+        <v>-0.5347</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3208</v>
@@ -766,13 +766,13 @@
         <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5734</v>
+        <v>0.8609</v>
       </c>
       <c r="T4" t="n">
-        <v>0.207</v>
+        <v>0.0023</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3664</v>
+        <v>0.8585</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5507</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.5882</v>
+        <v>-2.6047</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3443</v>
+        <v>-1.3485</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.244</v>
+        <v>-1.2562</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9855</v>
+        <v>-0.4815</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9550999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0304</v>
+        <v>-0.7275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3091</v>
+        <v>1.3987</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2687</v>
+        <v>0.7876</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0404</v>
+        <v>0.611</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2947</v>
+        <v>-1.8801</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2239</v>
+        <v>-0.5416</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0708</v>
+        <v>-1.3385</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2014</v>
+        <v>0.4643</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3258</v>
+        <v>0.1906</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1244</v>
+        <v>0.2738</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8199</v>
+        <v>-2.6593</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5102</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3096</v>
+        <v>-2.1103</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4815</v>
+        <v>-1.9855</v>
       </c>
       <c r="H6" t="n">
-        <v>0.246</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7275</v>
+        <v>-1.0304</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3987</v>
+        <v>0.3091</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7876</v>
+        <v>0.2687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.611</v>
+        <v>0.0404</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8801</v>
+        <v>-2.2947</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5416</v>
+        <v>-1.2239</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3385</v>
+        <v>-1.0708</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3709</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2491</v>
+        <v>0.1304</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0288</v>
+        <v>0.1212</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2203</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3603</v>
+        <v>-3.1137</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3613</v>
+        <v>-2.3019</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.999</v>
+        <v>-0.8119</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1449</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4506</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2664</v>
+        <v>0.3258</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1841</v>
+        <v>0.3713</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8825</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2195</v>
+        <v>-3.8707</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6371</v>
+        <v>-3.4754</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5824</v>
+        <v>-0.3953</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4034</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.641</v>
+        <v>-0.2922</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4158</v>
+        <v>-0.2541</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2252</v>
+        <v>-0.0381</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3676</v>
+        <v>-4.2326</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7761</v>
+        <v>-2.6143</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5915</v>
+        <v>-1.6182</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1809</v>
@@ -1156,13 +1156,13 @@
         <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.249</v>
+        <v>-0.114</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5346</v>
+        <v>-0.3729</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2857</v>
+        <v>0.2589</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6083</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8837</v>
+        <v>-4.7416</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1316</v>
+        <v>-2.8167</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7521</v>
+        <v>-1.925</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6382</v>
+        <v>-5.1303</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6931</v>
+        <v>-3.236</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9451</v>
+        <v>-1.8943</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2226</v>
+        <v>-2.7116</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1514</v>
+        <v>-1.4684</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0712</v>
+        <v>-1.2432</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4156</v>
+        <v>-2.4187</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5416</v>
+        <v>-1.7676</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8739</v>
+        <v>-0.6511</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2257</v>
+        <v>0.3471</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0288</v>
+        <v>-0.2088</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1969</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.492</v>
+        <v>1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.0415</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.492</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9288</v>
+        <v>-4.8289</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8167</v>
+        <v>-2.9698</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1121</v>
+        <v>-1.859</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.1303</v>
+        <v>-2.6382</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.236</v>
+        <v>-0.6931</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8943</v>
+        <v>-1.9451</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7116</v>
+        <v>-0.2226</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4684</v>
+        <v>-0.1514</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2432</v>
+        <v>-0.0712</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4187</v>
+        <v>-2.4156</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7676</v>
+        <v>-0.5416</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6511</v>
+        <v>-1.8739</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.16</v>
+        <v>0.2805</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2088</v>
+        <v>0.1906</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3688</v>
+        <v>0.09</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2166</v>
+        <v>-1.492</v>
       </c>
       <c r="W11" t="n">
-        <v>3.0415</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8249</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.3255</v>
+        <v>-18.0284</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5828</v>
+        <v>-7.285700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.7427</v>
+        <v>-10.7426</v>
       </c>
       <c r="G12" t="n">
         <v>-12.4683</v>
@@ -1360,16 +1360,16 @@
         <v>-3.072700000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.3955</v>
+        <v>-9.395500000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>7.692500000000002</v>
+        <v>7.6925</v>
       </c>
       <c r="K12" t="n">
-        <v>7.113999999999998</v>
+        <v>7.114000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5783</v>
+        <v>0.5782999999999995</v>
       </c>
       <c r="M12" t="n">
         <v>-20.1608</v>
@@ -1381,7 +1381,7 @@
         <v>-9.974</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.8546</v>
+        <v>-6.854599999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-22.5224</v>
@@ -1390,13 +1390,13 @@
         <v>15.6678</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9376</v>
+        <v>3.2345</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09719999999999993</v>
+        <v>0.1999999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0347</v>
+        <v>3.0348</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9401</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.5289</v>
+        <v>8.5418</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5188</v>
+        <v>6.8258</v>
       </c>
       <c r="F13" t="n">
-        <v>2.01</v>
+        <v>1.716</v>
       </c>
       <c r="G13" t="n">
         <v>7.5641</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8734</v>
+        <v>-0.5664</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9391</v>
+        <v>0.645</v>
       </c>
       <c r="V13" t="n">
         <v>1.0949</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6106</v>
+        <v>6.1314</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6665</v>
+        <v>5.9735</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0559</v>
+        <v>0.158</v>
       </c>
       <c r="G14" t="n">
         <v>4.7827</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3472</v>
+        <v>-0.8263</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6952</v>
+        <v>-0.3882</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.652</v>
+        <v>-0.4382</v>
       </c>
       <c r="V14" t="n">
         <v>0.6083</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3259</v>
+        <v>3.1968</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0519</v>
+        <v>-0.1542</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3777</v>
+        <v>3.351</v>
       </c>
       <c r="G15" t="n">
         <v>0.5194</v>
@@ -1624,13 +1624,13 @@
         <v>3.7211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0772</v>
+        <v>-0.2063</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1911</v>
+        <v>-0.2935</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1139</v>
+        <v>0.0872</v>
       </c>
       <c r="V15" t="n">
         <v>2.1003</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0374</v>
+        <v>1.8327</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7975</v>
+        <v>0.5928</v>
       </c>
       <c r="F16" t="n">
         <v>1.2399</v>
@@ -1702,10 +1702,10 @@
         <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4864</v>
+        <v>0.2817</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1653</v>
+        <v>-0.0394</v>
       </c>
       <c r="U16" t="n">
         <v>0.3211</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CACHOPAS GIL PRATES</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5152</v>
+        <v>1.5796</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8915</v>
+        <v>0.8306</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3763</v>
+        <v>0.749</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5535</v>
+        <v>2.2503</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4172</v>
+        <v>0.7145</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9707</v>
+        <v>1.5358</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9014</v>
+        <v>1.9024</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3318</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2332</v>
+        <v>1.2577</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3479</v>
+        <v>0.3479</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0853</v>
+        <v>0.0698</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2625</v>
+        <v>0.2781</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9792</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0122</v>
+        <v>-0.1573</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0306</v>
+        <v>-0.3299</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0184</v>
+        <v>0.1726</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0053</v>
+        <v>-0.1217</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0053</v>
+        <v>-1.3383</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>M. CACHOPAS GIL PRATES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3215</v>
+        <v>1.3151</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6259</v>
+        <v>1.5845</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6956</v>
+        <v>-0.2694</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2503</v>
+        <v>1.5535</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7145</v>
+        <v>-1.4172</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5358</v>
+        <v>2.9707</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9024</v>
+        <v>2.9014</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6447000000000001</v>
+        <v>-0.3318</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2577</v>
+        <v>3.2332</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3479</v>
+        <v>-1.3479</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0698</v>
+        <v>-1.0853</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2781</v>
+        <v>-0.2625</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3917</v>
+        <v>0.9792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4155</v>
+        <v>-0.2123</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5346</v>
+        <v>-0.3376</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1192</v>
+        <v>0.1253</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1217</v>
+        <v>-1.0053</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3383</v>
+        <v>-1.0053</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0304</v>
+        <v>0.9014</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8018</v>
+        <v>-0.9041</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8322</v>
+        <v>1.8055</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0633</v>
@@ -1936,13 +1936,13 @@
         <v>3.7211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4689</v>
+        <v>-0.598</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4464</v>
+        <v>-0.5487</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0225</v>
+        <v>-0.0493</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1792</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9092</v>
+        <v>0.829</v>
       </c>
       <c r="E20" t="n">
         <v>0.4722</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4369</v>
+        <v>0.3567</v>
       </c>
       <c r="G20" t="n">
         <v>1.0004</v>
@@ -2014,13 +2014,13 @@
         <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0117</v>
+        <v>-0.0919</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1071</v>
+        <v>0.0269</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2754</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8706</v>
+        <v>0.5903</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7991</v>
+        <v>-1.1061</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6697</v>
+        <v>1.6964</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1662</v>
@@ -2092,13 +2092,13 @@
         <v>2.3502</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2374</v>
+        <v>-0.5177</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1059</v>
+        <v>-0.2011</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3433</v>
+        <v>-0.3166</v>
       </c>
       <c r="V21" t="n">
         <v>1.8825</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2068</v>
+        <v>-2.1847</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5246</v>
+        <v>-0.4222</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6823</v>
+        <v>-1.7625</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7264</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6763</v>
+        <v>-0.6542</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4387</v>
+        <v>-0.5189</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0299</v>
+        <v>-2.8207</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0732</v>
+        <v>-1.9709</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9567</v>
+        <v>-0.8498</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9824000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>0.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2434</v>
+        <v>-0.0341</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0418</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2166</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.3255</v>
+        <v>18.3252</v>
       </c>
       <c r="E25" t="n">
-        <v>10.7426</v>
+        <v>10.7427</v>
       </c>
       <c r="F25" t="n">
         <v>7.582500000000001</v>
@@ -2407,10 +2407,10 @@
         <v>-2.9377</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.0347</v>
+        <v>-3.0348</v>
       </c>
       <c r="U25" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.09690000000000004</v>
       </c>
       <c r="V25" t="n">
         <v>1.9401</v>
